--- a/PhoneStore.AutoTests/ST-FunctionalTestCase-BDCLPM.xlsx
+++ b/PhoneStore.AutoTests/ST-FunctionalTestCase-BDCLPM.xlsx
@@ -5660,7 +5660,7 @@
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="75">
+  <fonts count="76">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6191,6 +6191,13 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color rgb="FF006400"/>
+      <name val="Arial"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="39">
@@ -8427,7 +8434,7 @@
     <xf numFmtId="0" fontId="27" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -12861,7 +12868,7 @@
       </c>
       <c r="M3" s="126">
         <f>COUNTIF(M7:M211,"PASSED")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3" s="122"/>
       <c r="O3" s="122"/>
@@ -13505,10 +13512,10 @@
       <c r="K26" s="144" t="s">
         <v>455</v>
       </c>
-      <c r="L26" s="335" t="s">
+      <c r="L26" s="144" t="s">
         <v>414</v>
       </c>
-      <c r="M26" s="336" t="s">
+      <c r="M26" s="151" t="s">
         <v>415</v>
       </c>
       <c r="N26" s="146"/>
@@ -13609,10 +13616,10 @@
       <c r="K30" s="144" t="s">
         <v>464</v>
       </c>
-      <c r="L30" s="335" t="s">
+      <c r="L30" s="144" t="s">
         <v>414</v>
       </c>
-      <c r="M30" s="336" t="s">
+      <c r="M30" s="151" t="s">
         <v>415</v>
       </c>
       <c r="N30" s="146"/>
@@ -13696,10 +13703,10 @@
       <c r="K33" s="144" t="s">
         <v>473</v>
       </c>
-      <c r="L33" s="335" t="s">
+      <c r="L33" s="144" t="s">
         <v>414</v>
       </c>
-      <c r="M33" s="336" t="s">
+      <c r="M33" s="151" t="s">
         <v>415</v>
       </c>
       <c r="N33" s="146"/>
@@ -13781,8 +13788,12 @@
       <c r="K36" s="144" t="s">
         <v>481</v>
       </c>
-      <c r="L36" s="144"/>
-      <c r="M36" s="144"/>
+      <c r="L36" s="144" t="s">
+        <v>414</v>
+      </c>
+      <c r="M36" s="151" t="s">
+        <v>415</v>
+      </c>
       <c r="N36" s="146"/>
       <c r="O36" s="146"/>
     </row>
@@ -13858,10 +13869,10 @@
       <c r="K39" s="144" t="s">
         <v>486</v>
       </c>
-      <c r="L39" s="335" t="s">
+      <c r="L39" s="144" t="s">
         <v>414</v>
       </c>
-      <c r="M39" s="336" t="s">
+      <c r="M39" s="151" t="s">
         <v>415</v>
       </c>
       <c r="N39" s="146"/>
@@ -16080,8 +16091,12 @@
       <c r="K121" s="144" t="s">
         <v>670</v>
       </c>
-      <c r="L121" s="144"/>
-      <c r="M121" s="144"/>
+      <c r="L121" s="335" t="s">
+        <v>414</v>
+      </c>
+      <c r="M121" s="336" t="s">
+        <v>415</v>
+      </c>
       <c r="N121" s="144"/>
       <c r="O121" s="144" t="s">
         <v>80</v>
@@ -16176,10 +16191,10 @@
       <c r="K125" s="144" t="s">
         <v>675</v>
       </c>
-      <c r="L125" s="335" t="s">
+      <c r="L125" s="144" t="s">
         <v>414</v>
       </c>
-      <c r="M125" s="336" t="s">
+      <c r="M125" s="151" t="s">
         <v>415</v>
       </c>
       <c r="N125" s="144"/>
